--- a/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/Tables/Signals_OLS_Results_Full_GDP.xlsx
+++ b/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/Tables/Signals_OLS_Results_Full_GDP.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfbe04e23282f0d1/Desktop/ifo/Konjunkturprognose Evaluierung/ifo_forecast_evaluation/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/Tables/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_23F921ED6FD30A0D532C4C11F50B444B6C2899DE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB4968D7-EA7A-4B08-9B9B-437BEA453ED2}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -115,8 +121,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,17 +181,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -223,7 +237,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -257,6 +271,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -291,9 +306,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -466,11 +482,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.54296875" customWidth="1"/>
+    <col min="2" max="2" width="38.08984375" customWidth="1"/>
+    <col min="3" max="3" width="40.54296875" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="9" max="9" width="39.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,7 +531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -519,16 +542,16 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>-0.04626454330400605</v>
+        <v>-0.60659832948691128</v>
       </c>
       <c r="E2">
-        <v>0.1433309020658017</v>
+        <v>0.12878965050145061</v>
       </c>
       <c r="F2">
-        <v>-0.322781358640766</v>
+        <v>-4.709992822599351</v>
       </c>
       <c r="G2">
-        <v>0.7483897421718806</v>
+        <v>2.4968174210081191E-5</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -537,16 +560,16 @@
         <v>25</v>
       </c>
       <c r="J2">
-        <v>7.029254283565114</v>
+        <v>56.398663192295693</v>
       </c>
       <c r="K2">
-        <v>0.00224341503618852</v>
+        <v>7.2195231771267259E-13</v>
       </c>
       <c r="L2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -557,16 +580,16 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>0.8874238067055383</v>
+        <v>1.1809487319957159</v>
       </c>
       <c r="E3">
-        <v>0.1121335330001217</v>
+        <v>0.1126569467427002</v>
       </c>
       <c r="F3">
-        <v>7.913991318766129</v>
+        <v>10.482697837470351</v>
       </c>
       <c r="G3">
-        <v>5.362718036737278E-10</v>
+        <v>1.529988930838052E-13</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -575,16 +598,16 @@
         <v>25</v>
       </c>
       <c r="J3">
-        <v>7.029254283565114</v>
+        <v>56.398663192295693</v>
       </c>
       <c r="K3">
-        <v>0.00224341503618852</v>
+        <v>7.2195231771267259E-13</v>
       </c>
       <c r="L3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -595,16 +618,16 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>0.1662223782653119</v>
+        <v>0.2334248544943488</v>
       </c>
       <c r="E4">
-        <v>0.1518904796965012</v>
+        <v>0.12598196937776029</v>
       </c>
       <c r="F4">
-        <v>1.09435679311467</v>
+        <v>1.8528433524833869</v>
       </c>
       <c r="G4">
-        <v>0.2797533406871878</v>
+        <v>7.0619190820838632E-2</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -613,16 +636,16 @@
         <v>26</v>
       </c>
       <c r="J4">
-        <v>185.0668723577883</v>
+        <v>321.16984714891959</v>
       </c>
       <c r="K4">
-        <v>3.791973168566011E-22</v>
+        <v>5.6506487252859653E-27</v>
       </c>
       <c r="L4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -633,16 +656,16 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>0.8448603317359519</v>
+        <v>0.81801236571299452</v>
       </c>
       <c r="E5">
-        <v>0.1188300350585438</v>
+        <v>0.110200966921414</v>
       </c>
       <c r="F5">
-        <v>7.109821446402131</v>
+        <v>7.4229145947179536</v>
       </c>
       <c r="G5">
-        <v>7.893873541469658E-09</v>
+        <v>2.756314401097213E-9</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -651,16 +674,16 @@
         <v>26</v>
       </c>
       <c r="J5">
-        <v>185.0668723577883</v>
+        <v>321.16984714891959</v>
       </c>
       <c r="K5">
-        <v>3.791973168566011E-22</v>
+        <v>5.6506487252859653E-27</v>
       </c>
       <c r="L5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -671,16 +694,16 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>-0.04420574103654296</v>
+        <v>-5.7922498404476823E-2</v>
       </c>
       <c r="E6">
-        <v>0.09526124666906238</v>
+        <v>9.378777496816712E-2</v>
       </c>
       <c r="F6">
-        <v>-0.4640474755711913</v>
+        <v>-0.61759113513607211</v>
       </c>
       <c r="G6">
-        <v>0.6449545328607009</v>
+        <v>0.54010198216955285</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -689,16 +712,16 @@
         <v>27</v>
       </c>
       <c r="J6">
-        <v>121.2494743032778</v>
+        <v>211.23022518483631</v>
       </c>
       <c r="K6">
-        <v>5.273189210468518E-21</v>
+        <v>9.5216769703955615E-26</v>
       </c>
       <c r="L6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -709,16 +732,16 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>0.1724909619840428</v>
+        <v>0.24807733197967419</v>
       </c>
       <c r="E7">
-        <v>0.1538573748532496</v>
+        <v>0.12907616038177019</v>
       </c>
       <c r="F7">
-        <v>1.12110948304276</v>
+        <v>1.921945394454968</v>
       </c>
       <c r="G7">
-        <v>0.2684634462485721</v>
+        <v>6.1255106831611748E-2</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -727,16 +750,16 @@
         <v>27</v>
       </c>
       <c r="J7">
-        <v>121.2494743032778</v>
+        <v>211.23022518483631</v>
       </c>
       <c r="K7">
-        <v>5.273189210468518E-21</v>
+        <v>9.5216769703955615E-26</v>
       </c>
       <c r="L7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -747,16 +770,16 @@
         <v>22</v>
       </c>
       <c r="D8">
-        <v>0.837720251412041</v>
+        <v>0.80591995659796067</v>
       </c>
       <c r="E8">
-        <v>0.1208871768623806</v>
+        <v>0.1126978010486567</v>
       </c>
       <c r="F8">
-        <v>6.929769336624607</v>
+        <v>7.1511595532375001</v>
       </c>
       <c r="G8">
-        <v>1.626386222235318E-08</v>
+        <v>7.7790193532952494E-9</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -765,16 +788,16 @@
         <v>27</v>
       </c>
       <c r="J8">
-        <v>121.2494743032778</v>
+        <v>211.23022518483631</v>
       </c>
       <c r="K8">
-        <v>5.273189210468518E-21</v>
+        <v>9.5216769703955615E-26</v>
       </c>
       <c r="L8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -785,16 +808,16 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>0.2337492553968256</v>
+        <v>0.17894690732645291</v>
       </c>
       <c r="E9">
-        <v>0.05333714449428291</v>
+        <v>4.4779916353938742E-2</v>
       </c>
       <c r="F9">
-        <v>4.382485369494812</v>
+        <v>3.996142063153119</v>
       </c>
       <c r="G9">
-        <v>6.954465277422782E-05</v>
+        <v>2.3608637842717901E-4</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -803,16 +826,16 @@
         <v>28</v>
       </c>
       <c r="J9">
-        <v>206.3869802509682</v>
+        <v>336.18313793395947</v>
       </c>
       <c r="K9">
-        <v>2.010608547341162E-18</v>
+        <v>1.662437303751017E-22</v>
       </c>
       <c r="L9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -823,16 +846,16 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>-0.08918987731766409</v>
+        <v>-0.15834645856022619</v>
       </c>
       <c r="E10">
-        <v>0.1213267600318091</v>
+        <v>0.1219046040257768</v>
       </c>
       <c r="F10">
-        <v>-0.7351212320701594</v>
+        <v>-1.298937475132143</v>
       </c>
       <c r="G10">
-        <v>0.4661660467773291</v>
+        <v>0.20073136552008111</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -841,16 +864,16 @@
         <v>29</v>
       </c>
       <c r="J10">
-        <v>102.4097496233831</v>
+        <v>171.50227732753669</v>
       </c>
       <c r="K10">
-        <v>2.795772474518327E-17</v>
+        <v>1.6834693157411099E-21</v>
       </c>
       <c r="L10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -861,16 +884,16 @@
         <v>22</v>
       </c>
       <c r="D11">
-        <v>0.2286132943635822</v>
+        <v>0.1792826725535108</v>
       </c>
       <c r="E11">
-        <v>0.05406494129856781</v>
+        <v>4.4442596740066481E-2</v>
       </c>
       <c r="F11">
-        <v>4.228494267682451</v>
+        <v>4.0340278404992818</v>
       </c>
       <c r="G11">
-        <v>0.0001170421863390278</v>
+        <v>2.1508178772782749E-4</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -879,16 +902,16 @@
         <v>29</v>
       </c>
       <c r="J11">
-        <v>102.4097496233831</v>
+        <v>171.50227732753669</v>
       </c>
       <c r="K11">
-        <v>2.795772474518327E-17</v>
+        <v>1.6834693157411099E-21</v>
       </c>
       <c r="L11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -899,16 +922,16 @@
         <v>23</v>
       </c>
       <c r="D12">
-        <v>-0.1075909174719541</v>
+        <v>-0.15014872885937819</v>
       </c>
       <c r="E12">
-        <v>0.1234268679892961</v>
+        <v>0.1265064366833957</v>
       </c>
       <c r="F12">
-        <v>-0.8716977042736326</v>
+        <v>-1.186886081023304</v>
       </c>
       <c r="G12">
-        <v>0.3882145357787764</v>
+        <v>0.2417884985608954</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -917,16 +940,16 @@
         <v>30</v>
       </c>
       <c r="J12">
-        <v>68.17935376283903</v>
+        <v>111.97479175964401</v>
       </c>
       <c r="K12">
-        <v>2.202846516637899E-16</v>
+        <v>2.4093542733722089E-20</v>
       </c>
       <c r="L12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -937,16 +960,16 @@
         <v>22</v>
       </c>
       <c r="D13">
-        <v>0.2518483419610838</v>
+        <v>0.18385727679393471</v>
       </c>
       <c r="E13">
-        <v>0.06030088408905533</v>
+        <v>4.7692339094434079E-2</v>
       </c>
       <c r="F13">
-        <v>4.176528184713539</v>
+        <v>3.8550693944762222</v>
       </c>
       <c r="G13">
-        <v>0.0001418531592747114</v>
+        <v>3.8147840394394479E-4</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -955,16 +978,16 @@
         <v>30</v>
       </c>
       <c r="J13">
-        <v>68.17935376283903</v>
+        <v>111.97479175964401</v>
       </c>
       <c r="K13">
-        <v>2.202846516637899E-16</v>
+        <v>2.4093542733722089E-20</v>
       </c>
       <c r="L13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -975,16 +998,16 @@
         <v>24</v>
       </c>
       <c r="D14">
-        <v>0.00499191384667007</v>
+        <v>-1.099262914235379E-3</v>
       </c>
       <c r="E14">
-        <v>0.00567630689911138</v>
+        <v>3.8544754027053452E-3</v>
       </c>
       <c r="F14">
-        <v>0.8794298714630016</v>
+        <v>-0.28519131642760981</v>
       </c>
       <c r="G14">
-        <v>0.3840565984025627</v>
+        <v>0.77686677251458314</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -993,16 +1016,16 @@
         <v>30</v>
       </c>
       <c r="J14">
-        <v>68.17935376283903</v>
+        <v>111.97479175964401</v>
       </c>
       <c r="K14">
-        <v>2.202846516637899E-16</v>
+        <v>2.4093542733722089E-20</v>
       </c>
       <c r="L14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1013,16 +1036,16 @@
         <v>21</v>
       </c>
       <c r="D15">
-        <v>-1.040938560335739</v>
+        <v>-1.0409385603357391</v>
       </c>
       <c r="E15">
-        <v>0.1487883699551412</v>
+        <v>0.14878836995514119</v>
       </c>
       <c r="F15">
-        <v>-6.996101648600458</v>
+        <v>-6.9961016486004581</v>
       </c>
       <c r="G15">
-        <v>1.158300276139004E-08</v>
+        <v>1.1583002761390041E-8</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1034,13 +1057,13 @@
         <v>106.2126959922786</v>
       </c>
       <c r="K15">
-        <v>1.441505371662022E-17</v>
+        <v>1.4415053716620219E-17</v>
       </c>
       <c r="L15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1054,7 +1077,7 @@
         <v>1.459158574429249</v>
       </c>
       <c r="E16">
-        <v>0.1398168412497099</v>
+        <v>0.13981684124970989</v>
       </c>
       <c r="F16">
         <v>10.43621470337199</v>
@@ -1072,13 +1095,13 @@
         <v>106.2126959922786</v>
       </c>
       <c r="K16">
-        <v>1.441505371662022E-17</v>
+        <v>1.4415053716620219E-17</v>
       </c>
       <c r="L16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1089,13 +1112,13 @@
         <v>21</v>
       </c>
       <c r="D17">
-        <v>0.1784279773118297</v>
+        <v>0.17842797731182969</v>
       </c>
       <c r="E17">
-        <v>0.1153015104929239</v>
+        <v>0.11530151049292391</v>
       </c>
       <c r="F17">
-        <v>1.547490371540101</v>
+        <v>1.5474903715401009</v>
       </c>
       <c r="G17">
         <v>0.1289082957763</v>
@@ -1107,16 +1130,16 @@
         <v>26</v>
       </c>
       <c r="J17">
-        <v>495.1945500606109</v>
+        <v>495.19455006061088</v>
       </c>
       <c r="K17">
-        <v>6.806319023250537E-31</v>
+        <v>6.8063190232505369E-31</v>
       </c>
       <c r="L17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1127,16 +1150,16 @@
         <v>22</v>
       </c>
       <c r="D18">
-        <v>0.8466077913927716</v>
+        <v>0.84660779139277165</v>
       </c>
       <c r="E18">
-        <v>0.1083491471363072</v>
+        <v>0.10834914713630719</v>
       </c>
       <c r="F18">
-        <v>7.813700557584531</v>
+        <v>7.8137005575845313</v>
       </c>
       <c r="G18">
-        <v>7.480282941006564E-10</v>
+        <v>7.4802829410065636E-10</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1145,16 +1168,16 @@
         <v>26</v>
       </c>
       <c r="J18">
-        <v>495.1945500606109</v>
+        <v>495.19455006061088</v>
       </c>
       <c r="K18">
-        <v>6.806319023250537E-31</v>
+        <v>6.8063190232505369E-31</v>
       </c>
       <c r="L18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1165,16 +1188,16 @@
         <v>23</v>
       </c>
       <c r="D19">
-        <v>-0.04766721194015083</v>
+        <v>-4.7667211940150833E-2</v>
       </c>
       <c r="E19">
-        <v>0.09459083768323853</v>
+        <v>9.4590837683238532E-2</v>
       </c>
       <c r="F19">
-        <v>-0.5039305402895005</v>
+        <v>-0.50393054028950046</v>
       </c>
       <c r="G19">
-        <v>0.6168824620533366</v>
+        <v>0.61688246205333663</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -1183,16 +1206,16 @@
         <v>27</v>
       </c>
       <c r="J19">
-        <v>324.6167444598867</v>
+        <v>324.61674445988672</v>
       </c>
       <c r="K19">
-        <v>1.516084267150936E-29</v>
+        <v>1.5160842671509361E-29</v>
       </c>
       <c r="L19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -1203,16 +1226,16 @@
         <v>21</v>
       </c>
       <c r="D20">
-        <v>0.1876892117019577</v>
+        <v>0.18768921170195771</v>
       </c>
       <c r="E20">
-        <v>0.1177348489515991</v>
+        <v>0.11773484895159909</v>
       </c>
       <c r="F20">
         <v>1.594168705130941</v>
       </c>
       <c r="G20">
-        <v>0.1182231975725685</v>
+        <v>0.11822319757256849</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -1221,16 +1244,16 @@
         <v>27</v>
       </c>
       <c r="J20">
-        <v>324.6167444598867</v>
+        <v>324.61674445988672</v>
       </c>
       <c r="K20">
-        <v>1.516084267150936E-29</v>
+        <v>1.5160842671509361E-29</v>
       </c>
       <c r="L20" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -1241,16 +1264,16 @@
         <v>22</v>
       </c>
       <c r="D21">
-        <v>0.8379520326292897</v>
+        <v>0.83795203262928974</v>
       </c>
       <c r="E21">
         <v>0.1106212267164933</v>
       </c>
       <c r="F21">
-        <v>7.574966012416798</v>
+        <v>7.5749660124167981</v>
       </c>
       <c r="G21">
-        <v>1.911195795193505E-09</v>
+        <v>1.911195795193505E-9</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1259,16 +1282,16 @@
         <v>27</v>
       </c>
       <c r="J21">
-        <v>324.6167444598867</v>
+        <v>324.61674445988672</v>
       </c>
       <c r="K21">
-        <v>1.516084267150936E-29</v>
+        <v>1.5160842671509361E-29</v>
       </c>
       <c r="L21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -1282,13 +1305,13 @@
         <v>0.1032483661119032</v>
       </c>
       <c r="E22">
-        <v>0.04245507451350289</v>
+        <v>4.2455074513502888E-2</v>
       </c>
       <c r="F22">
-        <v>2.431944056041285</v>
+        <v>2.4319440560412851</v>
       </c>
       <c r="G22">
-        <v>0.01906060580738938</v>
+        <v>1.9060605807389379E-2</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1297,7 +1320,7 @@
         <v>28</v>
       </c>
       <c r="J22">
-        <v>446.1543568378114</v>
+        <v>446.15435683781141</v>
       </c>
       <c r="K22">
         <v>5.46684728569085E-25</v>
@@ -1306,7 +1329,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1317,16 +1340,16 @@
         <v>23</v>
       </c>
       <c r="D23">
-        <v>-0.1495402897458608</v>
+        <v>-0.14954028974586081</v>
       </c>
       <c r="E23">
-        <v>0.1340718106258783</v>
+        <v>0.13407181062587831</v>
       </c>
       <c r="F23">
         <v>-1.115374582082334</v>
       </c>
       <c r="G23">
-        <v>0.2707448472038564</v>
+        <v>0.27074484720385639</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1338,13 +1361,13 @@
         <v>224.9090823906059</v>
       </c>
       <c r="K23">
-        <v>7.897389133240841E-24</v>
+        <v>7.8973891332408409E-24</v>
       </c>
       <c r="L23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -1355,16 +1378,16 @@
         <v>22</v>
       </c>
       <c r="D24">
-        <v>0.1023819355649355</v>
+        <v>0.10238193556493549</v>
       </c>
       <c r="E24">
-        <v>0.04234753709072949</v>
+        <v>4.2347537090729491E-2</v>
       </c>
       <c r="F24">
-        <v>2.417659741240264</v>
+        <v>2.4176597412402638</v>
       </c>
       <c r="G24">
-        <v>0.01983035818871359</v>
+        <v>1.9830358188713589E-2</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1376,13 +1399,13 @@
         <v>224.9090823906059</v>
       </c>
       <c r="K24">
-        <v>7.897389133240841E-24</v>
+        <v>7.8973891332408409E-24</v>
       </c>
       <c r="L24" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -1393,16 +1416,16 @@
         <v>23</v>
       </c>
       <c r="D25">
-        <v>-0.1895793002081571</v>
+        <v>-0.18957930020815711</v>
       </c>
       <c r="E25">
-        <v>0.1388369963928082</v>
+        <v>0.13883699639280819</v>
       </c>
       <c r="F25">
-        <v>-1.36548114071688</v>
+        <v>-1.3654811407168801</v>
       </c>
       <c r="G25">
-        <v>0.1792028907672165</v>
+        <v>0.17920289076721649</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1411,16 +1434,16 @@
         <v>30</v>
       </c>
       <c r="J25">
-        <v>150.9099963259519</v>
+        <v>150.90999632595191</v>
       </c>
       <c r="K25">
-        <v>7.570852925730141E-23</v>
+        <v>7.5708529257301412E-23</v>
       </c>
       <c r="L25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -1431,16 +1454,16 @@
         <v>22</v>
       </c>
       <c r="D26">
-        <v>0.07900372073871474</v>
+        <v>7.9003720738714742E-2</v>
       </c>
       <c r="E26">
-        <v>0.04746986912373327</v>
+        <v>4.7469869123733271E-2</v>
       </c>
       <c r="F26">
         <v>1.664291943438615</v>
       </c>
       <c r="G26">
-        <v>0.1033257944147137</v>
+        <v>0.10332579441471371</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1449,16 +1472,16 @@
         <v>30</v>
       </c>
       <c r="J26">
-        <v>150.9099963259519</v>
+        <v>150.90999632595191</v>
       </c>
       <c r="K26">
-        <v>7.570852925730141E-23</v>
+        <v>7.5708529257301412E-23</v>
       </c>
       <c r="L26" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -1469,16 +1492,16 @@
         <v>24</v>
       </c>
       <c r="D27">
-        <v>0.003859068471464291</v>
+        <v>3.859068471464291E-3</v>
       </c>
       <c r="E27">
-        <v>0.003567181673882985</v>
+        <v>3.567181673882985E-3</v>
       </c>
       <c r="F27">
         <v>1.081825604711514</v>
       </c>
       <c r="G27">
-        <v>0.2853598185041755</v>
+        <v>0.28535981850417552</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1487,16 +1510,16 @@
         <v>30</v>
       </c>
       <c r="J27">
-        <v>150.9099963259519</v>
+        <v>150.90999632595191</v>
       </c>
       <c r="K27">
-        <v>7.570852925730141E-23</v>
+        <v>7.5708529257301412E-23</v>
       </c>
       <c r="L27" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -1507,16 +1530,16 @@
         <v>21</v>
       </c>
       <c r="D28">
-        <v>-0.04028207947366687</v>
+        <v>-4.0282079473666868E-2</v>
       </c>
       <c r="E28">
         <v>0.1451297117517118</v>
       </c>
       <c r="F28">
-        <v>-0.2775591502764199</v>
+        <v>-0.27755915027641992</v>
       </c>
       <c r="G28">
-        <v>0.7826507921159737</v>
+        <v>0.78265079211597366</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1525,16 +1548,16 @@
         <v>25</v>
       </c>
       <c r="J28">
-        <v>3.82906894207194</v>
+        <v>3.8290689420719399</v>
       </c>
       <c r="K28">
-        <v>0.02930261947943145</v>
+        <v>2.9302619479431451E-2</v>
       </c>
       <c r="L28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -1545,16 +1568,16 @@
         <v>22</v>
       </c>
       <c r="D29">
-        <v>0.9157117682838848</v>
+        <v>0.91571176828388479</v>
       </c>
       <c r="E29">
-        <v>0.1125160302148658</v>
+        <v>0.11251603021486579</v>
       </c>
       <c r="F29">
-        <v>8.138500501085931</v>
+        <v>8.1385005010859306</v>
       </c>
       <c r="G29">
-        <v>2.55391141390271E-10</v>
+        <v>2.5539114139027099E-10</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1563,16 +1586,16 @@
         <v>25</v>
       </c>
       <c r="J29">
-        <v>3.82906894207194</v>
+        <v>3.8290689420719399</v>
       </c>
       <c r="K29">
-        <v>0.02930261947943145</v>
+        <v>2.9302619479431451E-2</v>
       </c>
       <c r="L29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -1589,10 +1612,10 @@
         <v>0.1521197204613611</v>
       </c>
       <c r="F30">
-        <v>0.6883053406081187</v>
+        <v>0.68830534060811865</v>
       </c>
       <c r="G30">
-        <v>0.4948736701570517</v>
+        <v>0.49487367015705169</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1601,16 +1624,16 @@
         <v>26</v>
       </c>
       <c r="J30">
-        <v>178.2245774590532</v>
+        <v>178.22457745905319</v>
       </c>
       <c r="K30">
-        <v>7.941755086402321E-22</v>
+        <v>7.9417550864023212E-22</v>
       </c>
       <c r="L30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -1621,16 +1644,16 @@
         <v>22</v>
       </c>
       <c r="D31">
-        <v>0.8718777470287556</v>
+        <v>0.87187774702875565</v>
       </c>
       <c r="E31">
         <v>0.117935237775359</v>
       </c>
       <c r="F31">
-        <v>7.392851903088483</v>
+        <v>7.3928519030884834</v>
       </c>
       <c r="G31">
-        <v>3.048564661046039E-09</v>
+        <v>3.0485646610460391E-9</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1639,16 +1662,16 @@
         <v>26</v>
       </c>
       <c r="J31">
-        <v>178.2245774590532</v>
+        <v>178.22457745905319</v>
       </c>
       <c r="K31">
-        <v>7.941755086402321E-22</v>
+        <v>7.9417550864023212E-22</v>
       </c>
       <c r="L31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -1659,13 +1682,13 @@
         <v>23</v>
       </c>
       <c r="D32">
-        <v>-0.04215495317664692</v>
+        <v>-4.2154953176646921E-2</v>
       </c>
       <c r="E32">
-        <v>0.09540066197951631</v>
+        <v>9.5400661979516313E-2</v>
       </c>
       <c r="F32">
-        <v>-0.441872753311692</v>
+        <v>-0.44187275331169201</v>
       </c>
       <c r="G32">
         <v>0.6607956576217775</v>
@@ -1680,13 +1703,13 @@
         <v>116.7083482705409</v>
       </c>
       <c r="K32">
-        <v>1.094767943370117E-20</v>
+        <v>1.0947679433701169E-20</v>
       </c>
       <c r="L32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -1697,16 +1720,16 @@
         <v>21</v>
       </c>
       <c r="D33">
-        <v>0.115906828780285</v>
+        <v>0.11590682878028501</v>
       </c>
       <c r="E33">
         <v>0.1556091600132698</v>
       </c>
       <c r="F33">
-        <v>0.7448586495190958</v>
+        <v>0.74485864951909575</v>
       </c>
       <c r="G33">
-        <v>0.4604090365646215</v>
+        <v>0.46040903656462151</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -1718,13 +1741,13 @@
         <v>116.7083482705409</v>
       </c>
       <c r="K33">
-        <v>1.094767943370117E-20</v>
+        <v>1.0947679433701169E-20</v>
       </c>
       <c r="L33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>14</v>
       </c>
@@ -1735,16 +1758,16 @@
         <v>22</v>
       </c>
       <c r="D34">
-        <v>0.8627785569944345</v>
+        <v>0.86277855699443451</v>
       </c>
       <c r="E34">
         <v>0.1207968981750047</v>
       </c>
       <c r="F34">
-        <v>7.142389995349738</v>
+        <v>7.1423899953497383</v>
       </c>
       <c r="G34">
-        <v>8.00923801024631E-09</v>
+        <v>8.00923801024631E-9</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -1756,13 +1779,13 @@
         <v>116.7083482705409</v>
       </c>
       <c r="K34">
-        <v>1.094767943370117E-20</v>
+        <v>1.0947679433701169E-20</v>
       </c>
       <c r="L34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -1773,16 +1796,16 @@
         <v>22</v>
       </c>
       <c r="D35">
-        <v>0.2259046361090463</v>
+        <v>0.22590463610904629</v>
       </c>
       <c r="E35">
-        <v>0.05704351297839359</v>
+        <v>5.7043512978393593E-2</v>
       </c>
       <c r="F35">
-        <v>3.960216058127633</v>
+        <v>3.9602160581276329</v>
       </c>
       <c r="G35">
-        <v>0.0002639468994835532</v>
+        <v>2.6394689948355322E-4</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1794,13 +1817,13 @@
         <v>184.1519857097953</v>
       </c>
       <c r="K35">
-        <v>1.63178955646664E-17</v>
+        <v>1.6317895564666401E-17</v>
       </c>
       <c r="L35" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -1814,13 +1837,13 @@
         <v>-0.1304584593924894</v>
       </c>
       <c r="E36">
-        <v>0.1231180941621497</v>
+        <v>0.12311809416214969</v>
       </c>
       <c r="F36">
         <v>-1.059620523533058</v>
       </c>
       <c r="G36">
-        <v>0.2950996075506032</v>
+        <v>0.29509960755060322</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1829,7 +1852,7 @@
         <v>29</v>
       </c>
       <c r="J36">
-        <v>92.88864694296437</v>
+        <v>92.888646942964371</v>
       </c>
       <c r="K36">
         <v>1.611396640941495E-16</v>
@@ -1838,7 +1861,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -1849,16 +1872,16 @@
         <v>22</v>
       </c>
       <c r="D37">
-        <v>0.2227581647195878</v>
+        <v>0.22275816471958779</v>
       </c>
       <c r="E37">
-        <v>0.05704318256868404</v>
+        <v>5.7043182568684042E-2</v>
       </c>
       <c r="F37">
         <v>3.905079532534343</v>
       </c>
       <c r="G37">
-        <v>0.00032011946900396</v>
+        <v>3.2011946900396002E-4</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -1867,7 +1890,7 @@
         <v>29</v>
       </c>
       <c r="J37">
-        <v>92.88864694296437</v>
+        <v>92.888646942964371</v>
       </c>
       <c r="K37">
         <v>1.611396640941495E-16</v>
@@ -1876,7 +1899,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -1887,7 +1910,7 @@
         <v>23</v>
       </c>
       <c r="D38">
-        <v>-0.1575304105705757</v>
+        <v>-0.15753041057057571</v>
       </c>
       <c r="E38">
         <v>0.1259407582786416</v>
@@ -1896,7 +1919,7 @@
         <v>-1.250829459213217</v>
       </c>
       <c r="G38">
-        <v>0.2177600835832535</v>
+        <v>0.21776008358325349</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -1905,16 +1928,16 @@
         <v>30</v>
       </c>
       <c r="J38">
-        <v>62.30830701081388</v>
+        <v>62.308307010813877</v>
       </c>
       <c r="K38">
-        <v>1.068685558925752E-15</v>
+        <v>1.0686855589257519E-15</v>
       </c>
       <c r="L38" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -1925,16 +1948,16 @@
         <v>22</v>
       </c>
       <c r="D39">
-        <v>0.2594713421733368</v>
+        <v>0.25947134217333678</v>
       </c>
       <c r="E39">
-        <v>0.06754729940433633</v>
+        <v>6.7547299404336333E-2</v>
       </c>
       <c r="F39">
         <v>3.841328142819572</v>
       </c>
       <c r="G39">
-        <v>0.0003976941211166144</v>
+        <v>3.9769412111661438E-4</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -1943,16 +1966,16 @@
         <v>30</v>
       </c>
       <c r="J39">
-        <v>62.30830701081388</v>
+        <v>62.308307010813877</v>
       </c>
       <c r="K39">
-        <v>1.068685558925752E-15</v>
+        <v>1.0686855589257519E-15</v>
       </c>
       <c r="L39" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -1963,16 +1986,16 @@
         <v>24</v>
       </c>
       <c r="D40">
-        <v>0.00669690298710842</v>
+        <v>6.6969029871084204E-3</v>
       </c>
       <c r="E40">
-        <v>0.006604206095404022</v>
+        <v>6.604206095404022E-3</v>
       </c>
       <c r="F40">
         <v>1.014036038604081</v>
       </c>
       <c r="G40">
-        <v>0.3162376049023772</v>
+        <v>0.31623760490237718</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -1981,10 +2004,10 @@
         <v>30</v>
       </c>
       <c r="J40">
-        <v>62.30830701081388</v>
+        <v>62.308307010813877</v>
       </c>
       <c r="K40">
-        <v>1.068685558925752E-15</v>
+        <v>1.0686855589257519E-15</v>
       </c>
       <c r="L40" t="s">
         <v>31</v>
